--- a/data/file_generation/reference/data_198/教师课程班级对应表_合并版_res.xlsx
+++ b/data/file_generation/reference/data_198/教师课程班级对应表_合并版_res.xlsx
@@ -6177,18 +6177,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28ABE119-C57F-4061-A01B-E47CE03AFABF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{547D36AD-A50B-4713-A98C-C947659D932A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63FD6BDF-792B-437D-895B-2CB13CEEA9AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0344BF90-77A6-4A25-91D5-C4E2AFD01E53}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B13C3DD5-46E7-45C1-88CE-FA47E24A880C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0AAE956-3B25-4A0C-970C-0829B7DC9FEC}"/>
 </file>